--- a/output/pdf_financials_xlsx/HFC.xlsx
+++ b/output/pdf_financials_xlsx/HFC.xlsx
@@ -4902,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.043</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>0.043</v>
@@ -4946,16 +4946,16 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.041697</v>
+        <v>0.129214</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>1.455</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.455</v>
+        <v>1.507</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1.681</v>
+        <v>1.733</v>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
@@ -4963,22 +4963,22 @@
         </is>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2.048</v>
+        <v>2.181</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2.126</v>
+        <v>2.181</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>2.258</v>
+        <v>2.362</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>2.257</v>
+        <v>2.51</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>2.187</v>
+        <v>2.44</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>2.427</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="93">
@@ -9076,7 +9076,11 @@
           <t>Warrants reserve (Note 16)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -10536,7 +10540,11 @@
           <t>Warrants reserve (Note 18)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12042,7 +12050,11 @@
           <t>Warrants reserve (Notes 12)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -13242,7 +13254,11 @@
           <t>Warrants reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -14520,7 +14536,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -15410,7 +15430,11 @@
           <t>Warrants reserve (Note 8 and 10)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -17330,7 +17354,11 @@
           <t>Warrants reserve (Notes 8 and 10)</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -18788,7 +18816,11 @@
           <t>Warrants reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HFC.xlsx
+++ b/output/pdf_financials_xlsx/HFC.xlsx
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002625</v>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.24115</v>
+        <v>-0.238525</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.24115</v>
+        <v>-0.238525</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
         <v>2.055542</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>2.014323</v>
+        <v>0.969</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.534</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -2131,22 +2131,22 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.207</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.182</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.222</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.946</v>
       </c>
     </row>
     <row r="35">
@@ -2211,13 +2211,13 @@
         <v>2.055542</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.014323</v>
+        <v>0.969</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.534</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -2225,22 +2225,22 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.207</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.182</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.222</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.946</v>
       </c>
     </row>
     <row r="37">
@@ -2775,13 +2775,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.262677</v>
+        <v>4.308</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.951</v>
+        <v>5.417</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.379</v>
+        <v>3.2</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -2789,22 +2789,22 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.762</v>
+        <v>5.517</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>12.599</v>
+        <v>10.392</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>10.069</v>
+        <v>5.887</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.247</v>
+        <v>3.743</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6396,19 +6396,19 @@
         </is>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.286</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.288</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.288</v>
       </c>
     </row>
     <row r="125">
@@ -6441,19 +6441,19 @@
         </is>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.286</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>2.528</v>
+        <v>2.24</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.288</v>
       </c>
     </row>
     <row r="126">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21866,7 +21866,11 @@
           <t>Lease payments (Note 20)</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -24494,7 +24498,11 @@
           <t>Lease payments (Note 23)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -27332,7 +27340,11 @@
           <t>Lease payments (Note 17)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -29636,7 +29648,11 @@
           <t>Lease payments (Note 16)</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HFC.xlsx
+++ b/output/pdf_financials_xlsx/HFC.xlsx
@@ -1864,10 +1864,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.161</v>
@@ -1917,10 +1917,10 @@
         <v>-2.632</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.293</v>
+        <v>1.445</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.286</v>
+        <v>1.438</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.619</v>
@@ -1972,10 +1972,10 @@
         <v>-26.98933552091878</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>8.167519423915104</v>
+        <v>9.12766091845114</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>7.481528884751876</v>
+        <v>8.36581534702426</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-30.0103128222757</v>
@@ -5316,19 +5316,19 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.451</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -19650,7 +19650,11 @@
           <t>Amortization - intangible asset (Note 12)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -19724,7 +19728,11 @@
           <t>Depreciation - right of use assets (Note 20)</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -19798,7 +19806,11 @@
           <t>Depreciation - property, plant and equipment</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -22912,7 +22924,11 @@
           <t>Amortization - intangible asset (Note 13)</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -22988,7 +23004,11 @@
           <t>Depreciation - right of use assets (Note 23)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -23062,7 +23082,11 @@
           <t>Depreciation - property, plant and equipment (Note 11)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -25330,7 +25354,11 @@
           <t>Depreciation - right of use assets (Note 17)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -25404,7 +25432,11 @@
           <t>Depreciation - property, plant and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -28238,7 +28270,11 @@
           <t>Depreciation - right of use assets (Note 16)</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
